--- a/task195/golden/screen_change_validation_2027q3.xlsx
+++ b/task195/golden/screen_change_validation_2027q3.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="90">
   <si>
     <t>Screen change adopted at the 0.030 cutoff for the quarter from 1 July 2027</t>
   </si>
@@ -269,15 +269,6 @@
   </si>
   <si>
     <t>L3</t>
-  </si>
-  <si>
-    <t>L4</t>
-  </si>
-  <si>
-    <t>L5</t>
-  </si>
-  <si>
-    <t>L6</t>
   </si>
   <si>
     <t>Source: dilution_panel_2027q1, prepared levels against replicate results.</t>
@@ -996,7 +987,7 @@
         <v>577</v>
       </c>
       <c r="D5" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1007,10 +998,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="7">
-        <v>588</v>
+        <v>598</v>
       </c>
       <c r="D6" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1021,10 +1012,10 @@
         <v>37</v>
       </c>
       <c r="C7" s="7">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="D7" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,10 +1026,10 @@
         <v>39</v>
       </c>
       <c r="C8" s="7">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="D8" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1049,10 +1040,10 @@
         <v>41</v>
       </c>
       <c r="C9" s="7">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="D9" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1063,10 +1054,10 @@
         <v>43</v>
       </c>
       <c r="C10" s="7">
-        <v>531</v>
+        <v>552</v>
       </c>
       <c r="D10" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1077,10 +1068,10 @@
         <v>45</v>
       </c>
       <c r="C11" s="7">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="D11" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1091,10 +1082,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="7">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="D12" s="7">
-        <v>5</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1105,10 +1096,10 @@
         <v>49</v>
       </c>
       <c r="C13" s="7">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="D13" s="7">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1341,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E056983-DA1E-53EF-99A9-A705F6A216E6}">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1400,13 +1391,13 @@
         <v>79</v>
       </c>
       <c r="B5" s="16">
-        <v>0.0077</v>
+        <v>0.0163</v>
       </c>
       <c r="C5" s="7">
         <v>9</v>
       </c>
       <c r="D5" s="17">
-        <v>0.961</v>
+        <v>0.865</v>
       </c>
       <c r="E5" s="7">
         <v>7</v>
@@ -1417,72 +1408,21 @@
         <v>80</v>
       </c>
       <c r="B6" s="16">
-        <v>0.0163</v>
+        <v>0.0629</v>
       </c>
       <c r="C6" s="7">
         <v>9</v>
       </c>
       <c r="D6" s="17">
-        <v>0.951</v>
+        <v>1.027</v>
       </c>
       <c r="E6" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="B7" s="16">
-        <v>0.0314</v>
-      </c>
-      <c r="C7" s="7">
-        <v>9</v>
-      </c>
-      <c r="D7" s="17">
-        <v>0.965</v>
-      </c>
-      <c r="E7" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B8" s="16">
-        <v>0.0629</v>
-      </c>
-      <c r="C8" s="7">
-        <v>9</v>
-      </c>
-      <c r="D8" s="17">
-        <v>1.008</v>
-      </c>
-      <c r="E8" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="16">
-        <v>0.1272</v>
-      </c>
-      <c r="C9" s="7">
-        <v>9</v>
-      </c>
-      <c r="D9" s="17">
-        <v>1.015</v>
-      </c>
-      <c r="E9" s="7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1500,42 +1440,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/task195/golden/screen_change_validation_2027q3.xlsx
+++ b/task195/golden/screen_change_validation_2027q3.xlsx
@@ -43,7 +43,7 @@
     <t>Increase at that cutoff</t>
   </si>
   <si>
-    <t>16 confirmed contamination events, 4.07 percentage points, 95 per cent interval 1.37 to 6.77 points</t>
+    <t>16 confirmed contamination events, 4.07 percentage points, 95 per cent interval clear of zero</t>
   </si>
   <si>
     <t>False-call rate</t>
@@ -118,10 +118,10 @@
     <t>Week ending</t>
   </si>
   <si>
-    <t>Specimens with a verdict</t>
-  </si>
-  <si>
-    <t>Difference against the report's total</t>
+    <t>Distinct vials the results came from</t>
+  </si>
+  <si>
+    <t>Excess of results issued over vials</t>
   </si>
   <si>
     <t>BA-2027-W13</t>
@@ -178,13 +178,13 @@
     <t>2027-05-28</t>
   </si>
   <si>
-    <t>The report's own total counts results issued, so a result sent again and a second aliquot typed again each add to it.</t>
+    <t>The report's own total counts results issued. Vials are counted on the biobank reference in specimen_request_crosswalk.tsv, because one vial can be booked in under more than one accession.</t>
   </si>
   <si>
     <t>Source: identity_panel_register_2027 against identity_panel_weekly_reports_2027.</t>
   </si>
   <si>
-    <t>Screen in service: flagged specimens per thousand released</t>
+    <t>Screen in service: flagged specimens per thousand specimens released</t>
   </si>
   <si>
     <t>The twelve reporting months to February 2027, from the quality-control warehouse extract.</t>
@@ -193,13 +193,13 @@
     <t>Reporting month</t>
   </si>
   <si>
-    <t>Specimens released</t>
+    <t>Specimens released, counted once each</t>
   </si>
   <si>
     <t>Flagged</t>
   </si>
   <si>
-    <t>Per thousand released</t>
+    <t>Per thousand specimens released</t>
   </si>
   <si>
     <t>2026-03</t>
@@ -244,7 +244,7 @@
     <t>Analytical sensitivity: recovery by prepared level, 2027Q1 panel</t>
   </si>
   <si>
-    <t>Nine replicates at each level, prepared 11 March 2027; voided replicates are not counted.</t>
+    <t>Nine replicates at each level, prepared 11 March 2027 from stock NS-27-04; voided replicates are not counted.</t>
   </si>
   <si>
     <t>Level</t>
@@ -984,10 +984,10 @@
         <v>33</v>
       </c>
       <c r="C5" s="7">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D5" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -998,10 +998,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="7">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D6" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1012,10 +1012,10 @@
         <v>37</v>
       </c>
       <c r="C7" s="7">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D7" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>39</v>
       </c>
       <c r="C8" s="7">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D8" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,10 @@
         <v>41</v>
       </c>
       <c r="C9" s="7">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D9" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1054,10 +1054,10 @@
         <v>43</v>
       </c>
       <c r="C10" s="7">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="D10" s="7">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1068,10 +1068,10 @@
         <v>45</v>
       </c>
       <c r="C11" s="7">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="D11" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1082,10 +1082,10 @@
         <v>47</v>
       </c>
       <c r="C12" s="7">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="D12" s="7">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,10 +1096,10 @@
         <v>49</v>
       </c>
       <c r="C13" s="7">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="D13" s="7">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1383,7 +1383,7 @@
         <v>0.878</v>
       </c>
       <c r="E4" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">

--- a/task195/golden/screen_change_validation_2027q3.xlsx
+++ b/task195/golden/screen_change_validation_2027q3.xlsx
@@ -1380,10 +1380,10 @@
         <v>9</v>
       </c>
       <c r="D4" s="17">
-        <v>0.878</v>
+        <v>1</v>
       </c>
       <c r="E4" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">

--- a/task195/golden/screen_change_validation_2027q3.xlsx
+++ b/task195/golden/screen_change_validation_2027q3.xlsx
@@ -1374,16 +1374,16 @@
         <v>78</v>
       </c>
       <c r="B4" s="16">
-        <v>0.0041</v>
+        <v>0.0081</v>
       </c>
       <c r="C4" s="7">
         <v>9</v>
       </c>
       <c r="D4" s="17">
-        <v>1</v>
+        <v>0.963</v>
       </c>
       <c r="E4" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
